--- a/2.1论文.xlsx
+++ b/2.1论文.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nijian.15/projects/MemFinRobot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B42B0EE8-6F78-3E45-9B84-FDEF5BEAAE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C96CBDD-0FE3-D543-BB09-5405E212F431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1000" yWindow="820" windowWidth="28240" windowHeight="17440" activeTab="1" xr2:uid="{E34BFDBD-D46F-5F40-9913-46C44D0BEDCA}"/>
+    <workbookView xWindow="2000" yWindow="820" windowWidth="28240" windowHeight="17440" activeTab="2" xr2:uid="{E34BFDBD-D46F-5F40-9913-46C44D0BEDCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="2.2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
   <si>
     <t>bibtex</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -460,12 +461,88 @@
     <t>A Survey on Large Language Model based Autonomous Agents - Science Explorer Abstract</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>@incollection{atkinson1968human,
+  title={Human memory: A proposed system and its control processes},
+  author={Atkinson, Richard C and Shiffrin, Richard M},
+  booktitle={The Psychology of Learning and Motivation: Advances in Research and Theory},
+  editor={Spence, Kenneth W and Spence, Janet T},
+  volume={2},
+  pages={89--195},
+  year={1968},
+  publisher={Academic Press},
+  address={New York, NY, USA},
+  doi={10.1016/S0079-7421(08)60422-3},
+  url={https://www.sciencedirect.com/science/chapter/bookseries/pii/S0079742108604223}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/chapter/bookseries/pii/S0079742108604223</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@article{baddeley2000episodic,
+  title={The episodic buffer: A new component of working memory},
+  author={Baddeley, Alan},
+  journal={Trends in Cognitive Sciences},
+  volume={4},
+  number={11},
+  pages={417--423},
+  year={2000},
+  publisher={Elsevier},
+  doi={10.1016/S1364-6613(00)01538-2},
+  url={https://www.sciencedirect.com/science/article/pii/S1364661300015382}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S1364661300015382</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@article{squire2004memory,
+  title={Memory systems of the brain: A brief history and current perspective},
+  author={Squire, Larry R},
+  journal={Neurobiology of Learning and Memory},
+  volume={82},
+  number={3},
+  pages={171--177},
+  year={2004},
+  publisher={Elsevier},
+  doi={10.1016/j.nlm.2004.06.006},
+  url={https://www.sciencedirect.com/science/article/pii/S1074742704000735}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>@incollection{tulving1972episodic,
+  title={Episodic and semantic memory},
+  author={Tulving, Endel},
+  booktitle={Organization of Memory},
+  editor={Tulving, Endel and Donaldson, Wayne},
+  pages={381--403},
+  year={1972},
+  publisher={Academic Press},
+  address={New York, NY, USA},
+  doi={10.1016/S0028-3932(20)30037-3},
+  url={https://www.sciencedirect.com/science/article/pii/S0028393220300373}
+}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S1074742704000735</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S0028393220300373</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -522,6 +599,12 @@
       <family val="1"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFAAA0FA"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -548,7 +631,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -566,6 +649,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1300,4 +1389,103 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B73C5EF9-C607-484F-BD34-B6F6675673B9}">
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="65.83203125" customWidth="1"/>
+    <col min="3" max="3" width="44.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="272">
+      <c r="B2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="238">
+      <c r="B3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="255">
+      <c r="B4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="238">
+      <c r="B5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" s="1"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" s="1"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{AB9B0D9A-B663-3E48-A50C-7A2DE93ED378}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{5E8FF9BB-4B5B-9C40-BD2E-53467A965258}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{3053BDB6-0FB2-4843-8AA2-9E04EAAEC707}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>